--- a/healthcare_forms/032_precision_nutrition_research_initiative_application_form--healthcare_forms.xlsx
+++ b/healthcare_forms/032_precision_nutrition_research_initiative_application_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>research_focus_other</t>
+          <t>research_focus_other_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Research Focus Other 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Funding Source Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>funding_source_other</t>
+          <t>funding_source_other_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Funding Source Other 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>funding_source_other</t>
+          <t>funding_source_other_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Funding Source Other 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nutrigenomics</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nutrigenomics</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>research_focus_choices</t>
+          <t>research_focus_human_nutrition_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>research_focus_human_nutrition_choices</t>
+          <t>research_focus_nutrigenomics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1267,63 +1267,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>research_focus_nutrigenomics_choices</t>
+          <t>research_focus_other_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>research_focus_other_choices</t>
+          <t>research_focus_other_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>research_focus_other_choices</t>
+          <t>funding_source_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>funding_source_choices</t>
+          <t>funding_source_foundation_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>funding_source_foundation_choices</t>
+          <t>funding_source_government_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,63 +1403,63 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>funding_source_government_choices</t>
+          <t>funding_source_other_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>funding_source_other_choices</t>
+          <t>funding_source_other_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>funding_source_other_choices</t>
+          <t>funding_source_grant_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>funding_source_grant_choices</t>
+          <t>funding_source_industry_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>funding_source_industry_choices</t>
+          <t>funding_source_investor_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>funding_source_investor_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>project_status_choices</t>
+          <t>project_status_active_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>project_status_active_choices</t>
+          <t>project_status_inactive_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1641,27 +1641,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>project_status_inactive_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
